--- a/resources/templates/standard/M1200-06.xlsx
+++ b/resources/templates/standard/M1200-06.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>낙하품 처리 관리대장</t>
   </si>
@@ -559,12 +562,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.9" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -709,22 +714,22 @@
     </row>
     <row r="4" ht="34.9" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
@@ -732,22 +737,22 @@
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
       <c r="S4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
       <c r="V4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
       <c r="Y4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
@@ -756,7 +761,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG4" s="4"/>
       <c r="AH4" s="4"/>
@@ -768,13 +773,13 @@
       <c r="AN4" s="4"/>
       <c r="AO4" s="4"/>
       <c r="AP4" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ4" s="4"/>
       <c r="AR4" s="4"/>
       <c r="AS4" s="4"/>
       <c r="AT4" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU4" s="4"/>
     </row>
@@ -811,14 +816,14 @@
       <c r="AD5" s="7"/>
       <c r="AE5" s="7"/>
       <c r="AF5" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG5" s="9"/>
       <c r="AH5" s="9"/>
       <c r="AI5" s="9"/>
       <c r="AJ5" s="9"/>
       <c r="AK5" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL5" s="9"/>
       <c r="AM5" s="9"/>
@@ -864,7 +869,7 @@
       <c r="AD6" s="7"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG6" s="10"/>
       <c r="AH6" s="9"/>
@@ -920,7 +925,7 @@
       <c r="AI7" s="9"/>
       <c r="AJ7" s="9"/>
       <c r="AK7" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL7" s="9"/>
       <c r="AM7" s="9"/>
@@ -966,7 +971,7 @@
       <c r="AD8" s="7"/>
       <c r="AE8" s="7"/>
       <c r="AF8" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG8" s="10"/>
       <c r="AH8" s="9"/>
@@ -1022,7 +1027,7 @@
       <c r="AI9" s="9"/>
       <c r="AJ9" s="9"/>
       <c r="AK9" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL9" s="9"/>
       <c r="AM9" s="9"/>
@@ -1068,7 +1073,7 @@
       <c r="AD10" s="7"/>
       <c r="AE10" s="7"/>
       <c r="AF10" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG10" s="10"/>
       <c r="AH10" s="9"/>
@@ -1124,7 +1129,7 @@
       <c r="AI11" s="9"/>
       <c r="AJ11" s="9"/>
       <c r="AK11" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL11" s="9"/>
       <c r="AM11" s="9"/>
@@ -1170,7 +1175,7 @@
       <c r="AD12" s="7"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG12" s="10"/>
       <c r="AH12" s="9"/>
@@ -1226,7 +1231,7 @@
       <c r="AI13" s="9"/>
       <c r="AJ13" s="9"/>
       <c r="AK13" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL13" s="9"/>
       <c r="AM13" s="9"/>
@@ -1272,7 +1277,7 @@
       <c r="AD14" s="7"/>
       <c r="AE14" s="7"/>
       <c r="AF14" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG14" s="10"/>
       <c r="AH14" s="9"/>
@@ -1328,7 +1333,7 @@
       <c r="AI15" s="9"/>
       <c r="AJ15" s="9"/>
       <c r="AK15" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL15" s="9"/>
       <c r="AM15" s="9"/>
@@ -1374,7 +1379,7 @@
       <c r="AD16" s="7"/>
       <c r="AE16" s="7"/>
       <c r="AF16" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG16" s="10"/>
       <c r="AH16" s="9"/>
@@ -1430,7 +1435,7 @@
       <c r="AI17" s="9"/>
       <c r="AJ17" s="9"/>
       <c r="AK17" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL17" s="9"/>
       <c r="AM17" s="9"/>
@@ -1476,7 +1481,7 @@
       <c r="AD18" s="7"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG18" s="10"/>
       <c r="AH18" s="9"/>
@@ -1532,7 +1537,7 @@
       <c r="AI19" s="9"/>
       <c r="AJ19" s="9"/>
       <c r="AK19" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL19" s="9"/>
       <c r="AM19" s="9"/>
@@ -1578,7 +1583,7 @@
       <c r="AD20" s="7"/>
       <c r="AE20" s="7"/>
       <c r="AF20" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG20" s="11"/>
       <c r="AH20" s="12"/>
